--- a/Okta.xlsx
+++ b/Okta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ken\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE98D0B-ABC5-43FA-8168-C08C6BD44D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45799601-F4C9-40CC-92C2-EAECB3193D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1485" yWindow="1020" windowWidth="27315" windowHeight="14580" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pin" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,9 @@
     <sheet name="③回目" sheetId="5" r:id="rId5"/>
     <sheet name="カスタム" sheetId="6" r:id="rId6"/>
     <sheet name="任意" sheetId="7" r:id="rId7"/>
+    <sheet name="任意２認証ー第１回目" sheetId="8" r:id="rId8"/>
+    <sheet name="任意２認証ー第２回目" sheetId="9" r:id="rId9"/>
+    <sheet name="認証のボタン" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -1578,6 +1581,50 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>383063</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>48819</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E82D47F5-89B9-2209-B3A4-AFF24148C9B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15773400" y="361950"/>
+          <a:ext cx="14784863" cy="8554644"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1982,6 +2029,1407 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>315805</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>19760</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24AAAD49-359F-5A07-BC98-F316DB433DEF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="10602805" cy="5087060"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>391920</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>162781</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EFA60A7-0784-9807-77CA-E4D3A4925D15}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="5791200"/>
+          <a:ext cx="9993120" cy="6134956"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>77551</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>105800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A506E53-A156-9326-4F2B-C9FB671796CB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="12487275"/>
+          <a:ext cx="9678751" cy="7344800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>373154</xdr:colOff>
+      <xdr:row>155</xdr:row>
+      <xdr:rowOff>67695</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="图片 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F98503A-78E7-80CE-614F-A1D8F56FD9EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="20812125"/>
+          <a:ext cx="12031754" cy="7306695"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>138</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>142</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="流程图: 过程 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3311C263-E464-232F-CE7D-58E3E795B898}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5200650" y="24974550"/>
+          <a:ext cx="2200275" cy="762000"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>158</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>96795</xdr:colOff>
+      <xdr:row>195</xdr:row>
+      <xdr:rowOff>172409</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="图片 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2067535-5713-DD56-7378-20E8B6CAE891}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="28594050"/>
+          <a:ext cx="11069595" cy="6868484"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>198</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>325427</xdr:colOff>
+      <xdr:row>244</xdr:row>
+      <xdr:rowOff>48794</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="图片 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B714C33E-598B-ABF9-B2BA-76C5F4BEE0F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="35833050"/>
+          <a:ext cx="11298227" cy="8373644"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>266701</xdr:colOff>
+      <xdr:row>181</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>266701</xdr:colOff>
+      <xdr:row>183</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="流程图: 过程 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C16F8EF9-1E47-40C5-8816-65AFBD0FB6C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4381501" y="32756475"/>
+          <a:ext cx="2057400" cy="428625"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>276224</xdr:colOff>
+      <xdr:row>214</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>552449</xdr:colOff>
+      <xdr:row>217</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="流程图: 过程 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{149D702D-1CFE-4ACE-8375-09E12E10CC7C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4391024" y="38881050"/>
+          <a:ext cx="3705225" cy="523875"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>247</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>477848</xdr:colOff>
+      <xdr:row>286</xdr:row>
+      <xdr:rowOff>172459</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="图片 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0D2E1A4-F7D2-5B9C-2143-D54652CC140E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="44700825"/>
+          <a:ext cx="11450648" cy="7230484"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>230163</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>10360</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F2C9298-A7CB-59F4-4865-6E082C1819E0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="11202963" cy="5982535"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>611105</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>115264</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D94CC0BE-DC95-F3F5-58BE-B606849B7BA3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="114300" y="6781800"/>
+          <a:ext cx="10783805" cy="6906589"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>77551</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>105800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2444663-8FE2-4E98-9BD1-8F8BE9287C4A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="14478000"/>
+          <a:ext cx="9678751" cy="7344800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>20776</xdr:colOff>
+      <xdr:row>170</xdr:row>
+      <xdr:rowOff>10436</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="图片 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{024E131E-FEE7-CBBE-5C88-D451BF7CB298}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2057400" y="24250650"/>
+          <a:ext cx="12365176" cy="6525536"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>276226</xdr:colOff>
+      <xdr:row>154</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>295276</xdr:colOff>
+      <xdr:row>156</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="流程图: 过程 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F31D648-38A5-4A76-AF33-03B1DB0CFC16}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7134226" y="27879675"/>
+          <a:ext cx="2076450" cy="523875"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>193</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>125565</xdr:colOff>
+      <xdr:row>227</xdr:row>
+      <xdr:rowOff>143754</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="图片 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4CA0E0F-0C5C-BFBC-4F6F-CD6A831691E2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2057400" y="34928175"/>
+          <a:ext cx="12469965" cy="6296904"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>232</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>68407</xdr:colOff>
+      <xdr:row>273</xdr:row>
+      <xdr:rowOff>48667</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="图片 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68FD9708-6809-4947-85D5-A02C867721AC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2057400" y="41986200"/>
+          <a:ext cx="12412807" cy="7468642"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>392111</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>105623</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B4AB5C3-94C0-EEA0-5FC2-F283B85E0A0B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="11364911" cy="6077798"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>325331</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>19911</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90950884-AC5D-9DE3-D1A8-ABC565749528}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="6515100"/>
+          <a:ext cx="10612331" cy="6173061"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>287226</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>153255</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B879C22-55E5-44A5-4E6B-669DCD17280B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="13211175"/>
+          <a:ext cx="10574226" cy="6125430"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>477944</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>58168</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C766EA5F-8E10-1230-AB33-783612CFD493}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="19726275"/>
+          <a:ext cx="12136544" cy="7297168"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>153</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>163479</xdr:colOff>
+      <xdr:row>194</xdr:row>
+      <xdr:rowOff>77246</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="图片 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A06B419A-CBD6-281D-74E8-FA0BDD0E29DD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="27689175"/>
+          <a:ext cx="11136279" cy="7497221"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>95251</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>9526</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="流程图: 过程 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09909C54-A33E-436A-9F0B-1EE6080BF9F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2533650" y="3714751"/>
+          <a:ext cx="857250" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="流程图: 过程 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A133E54-B9F4-4878-82DE-B2F57CF1D96E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4524375" y="9248775"/>
+          <a:ext cx="2076450" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="流程图: 过程 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{079CE26D-CCEB-4224-882F-02EF0D26201B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3667125" y="16430625"/>
+          <a:ext cx="1695450" cy="390525"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="流程图: 过程 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1383FE05-C62C-4D27-B2DF-69C8EC654658}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3952875" y="22831425"/>
+          <a:ext cx="2381250" cy="533400"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>168</xdr:row>
+      <xdr:rowOff>133351</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>170</xdr:row>
+      <xdr:rowOff>152401</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="流程图: 过程 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{859E49C9-4D5F-493E-B972-79790F552C54}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4514850" y="30537151"/>
+          <a:ext cx="2009775" cy="381000"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2472,6 +3920,17 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2C409B-D4F4-492B-BCA0-5439497FD164}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D062A18-3AEF-4F08-8DC4-DD15E865F6A3}">
   <dimension ref="A1"/>
@@ -2536,4 +3995,26 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4478571C-EE7D-4431-9D34-7AC05E66D83C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50AA6473-453D-4A3F-952D-FA7A01E7B8F6}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>